--- a/data_processed/CAR_clean.xlsx
+++ b/data_processed/CAR_clean.xlsx
@@ -610,7 +610,7 @@
         <v>42370</v>
       </c>
       <c r="B14" t="n">
-        <v>15.6</v>
+        <v>12.31</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         <v>42401</v>
       </c>
       <c r="B15" t="n">
-        <v>13.81</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -636,7 +636,7 @@
         <v>42430</v>
       </c>
       <c r="B16" t="n">
-        <v>7.37</v>
+        <v>11.94</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         <v>42461</v>
       </c>
       <c r="B17" t="n">
-        <v>8.35</v>
+        <v>12.03</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>42491</v>
       </c>
       <c r="B18" t="n">
-        <v>7.84</v>
+        <v>12.74</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
         <v>42522</v>
       </c>
       <c r="B19" t="n">
-        <v>7.66</v>
+        <v>12.54</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         <v>42552</v>
       </c>
       <c r="B20" t="n">
-        <v>9.029999999999999</v>
+        <v>13.03</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         <v>42583</v>
       </c>
       <c r="B21" t="n">
-        <v>8.029999999999999</v>
+        <v>13.83782270203328</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>42614</v>
       </c>
       <c r="B22" t="n">
-        <v>7.88</v>
+        <v>13.90493588360554</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>42644</v>
       </c>
       <c r="B23" t="n">
-        <v>7.09</v>
+        <v>14.22367849768678</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         <v>42675</v>
       </c>
       <c r="B24" t="n">
-        <v>9.9</v>
+        <v>13.4537887530114</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>42705</v>
       </c>
       <c r="B25" t="n">
-        <v>8.92</v>
+        <v>13.34</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>42736</v>
       </c>
       <c r="B26" t="n">
-        <v>15.6</v>
+        <v>12.69</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>42767</v>
       </c>
       <c r="B27" t="n">
-        <v>13.81</v>
+        <v>12.65</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>42795</v>
       </c>
       <c r="B28" t="n">
-        <v>7.37</v>
+        <v>12.85</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>42826</v>
       </c>
       <c r="B29" t="n">
-        <v>8.35</v>
+        <v>13.72</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>42856</v>
       </c>
       <c r="B30" t="n">
-        <v>7.84</v>
+        <v>13.7666146169185</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>42887</v>
       </c>
       <c r="B31" t="n">
-        <v>7.66</v>
+        <v>13.11</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>42917</v>
       </c>
       <c r="B32" t="n">
-        <v>9.029999999999999</v>
+        <v>12.42</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>42948</v>
       </c>
       <c r="B33" t="n">
-        <v>8.029999999999999</v>
+        <v>15.35</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         <v>42979</v>
       </c>
       <c r="B34" t="n">
-        <v>7.88</v>
+        <v>15.41</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>43009</v>
       </c>
       <c r="B35" t="n">
-        <v>7.09</v>
+        <v>15.27</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>43040</v>
       </c>
       <c r="B36" t="n">
-        <v>9.9</v>
+        <v>15.03</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>43070</v>
       </c>
       <c r="B37" t="n">
-        <v>8.92</v>
+        <v>15.35</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>43101</v>
       </c>
       <c r="B38" t="n">
-        <v>15.6</v>
+        <v>16.1</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>43132</v>
       </c>
       <c r="B39" t="n">
-        <v>13.81</v>
+        <v>16.25</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>43160</v>
       </c>
       <c r="B40" t="n">
-        <v>7.37</v>
+        <v>16.91</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>43191</v>
       </c>
       <c r="B41" t="n">
-        <v>8.35</v>
+        <v>16.49</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>43221</v>
       </c>
       <c r="B42" t="n">
-        <v>7.84</v>
+        <v>17.06</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>43252</v>
       </c>
       <c r="B43" t="n">
-        <v>7.66</v>
+        <v>16.34</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>43282</v>
       </c>
       <c r="B44" t="n">
-        <v>9.029999999999999</v>
+        <v>16.44</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>43313</v>
       </c>
       <c r="B45" t="n">
-        <v>8.029999999999999</v>
+        <v>16.39</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>43344</v>
       </c>
       <c r="B46" t="n">
-        <v>7.88</v>
+        <v>16.15</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>43374</v>
       </c>
       <c r="B47" t="n">
-        <v>7.09</v>
+        <v>15.73</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>43405</v>
       </c>
       <c r="B48" t="n">
-        <v>9.9</v>
+        <v>15.84</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>43435</v>
       </c>
       <c r="B49" t="n">
-        <v>8.92</v>
+        <v>15.52</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>43466</v>
       </c>
       <c r="B50" t="n">
-        <v>15.6</v>
+        <v>16.18</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>43497</v>
       </c>
       <c r="B51" t="n">
-        <v>13.81</v>
+        <v>16.52</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>43525</v>
       </c>
       <c r="B52" t="n">
-        <v>7.37</v>
+        <v>16.93</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>43556</v>
       </c>
       <c r="B53" t="n">
-        <v>8.35</v>
+        <v>16.96</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>43586</v>
       </c>
       <c r="B54" t="n">
-        <v>7.84</v>
+        <v>16.21</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>43617</v>
       </c>
       <c r="B55" t="n">
-        <v>7.66</v>
+        <v>17.65</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>43647</v>
       </c>
       <c r="B56" t="n">
-        <v>9.029999999999999</v>
+        <v>17.47</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>43678</v>
       </c>
       <c r="B57" t="n">
-        <v>8.029999999999999</v>
+        <v>17.42</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>43709</v>
       </c>
       <c r="B58" t="n">
-        <v>7.88</v>
+        <v>18</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>43739</v>
       </c>
       <c r="B59" t="n">
-        <v>7.09</v>
+        <v>18.43</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>43770</v>
       </c>
       <c r="B60" t="n">
-        <v>9.9</v>
+        <v>18.59</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>43800</v>
       </c>
       <c r="B61" t="n">
-        <v>8.92</v>
+        <v>18.72</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>43831</v>
       </c>
       <c r="B62" t="n">
-        <v>15.6</v>
+        <v>19.66</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>43862</v>
       </c>
       <c r="B63" t="n">
-        <v>13.81</v>
+        <v>20.31</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>43891</v>
       </c>
       <c r="B64" t="n">
-        <v>7.37</v>
+        <v>20.12</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>43922</v>
       </c>
       <c r="B65" t="n">
-        <v>8.35</v>
+        <v>19.29</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>43952</v>
       </c>
       <c r="B66" t="n">
-        <v>7.84</v>
+        <v>19.7</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>43983</v>
       </c>
       <c r="B67" t="n">
-        <v>7.66</v>
+        <v>22.17</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>44013</v>
       </c>
       <c r="B68" t="n">
-        <v>9.029999999999999</v>
+        <v>21.91</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>44044</v>
       </c>
       <c r="B69" t="n">
-        <v>8.029999999999999</v>
+        <v>21.52</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>44075</v>
       </c>
       <c r="B70" t="n">
-        <v>7.88</v>
+        <v>21.44</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>44105</v>
       </c>
       <c r="B71" t="n">
-        <v>7.09</v>
+        <v>21.91</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>44136</v>
       </c>
       <c r="B72" t="n">
-        <v>9.9</v>
+        <v>21.76</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>44166</v>
       </c>
       <c r="B73" t="n">
-        <v>8.92</v>
+        <v>21.63</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>44197</v>
       </c>
       <c r="B74" t="n">
-        <v>15.6</v>
+        <v>21.98</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>44228</v>
       </c>
       <c r="B75" t="n">
-        <v>13.81</v>
+        <v>21.39</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>44256</v>
       </c>
       <c r="B76" t="n">
-        <v>7.37</v>
+        <v>22.36</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>44287</v>
       </c>
       <c r="B77" t="n">
-        <v>8.35</v>
+        <v>22.59</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>44317</v>
       </c>
       <c r="B78" t="n">
-        <v>7.84</v>
+        <v>23.02</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>44348</v>
       </c>
       <c r="B79" t="n">
-        <v>7.66</v>
+        <v>22.64</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>44378</v>
       </c>
       <c r="B80" t="n">
-        <v>9.029999999999999</v>
+        <v>21.65</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44409</v>
       </c>
       <c r="B81" t="n">
-        <v>8.029999999999999</v>
+        <v>21.72</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>44440</v>
       </c>
       <c r="B82" t="n">
-        <v>7.88</v>
+        <v>21.29</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>44470</v>
       </c>
       <c r="B83" t="n">
-        <v>7.09</v>
+        <v>21.59</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44501</v>
       </c>
       <c r="B84" t="n">
-        <v>9.9</v>
+        <v>21.69</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>44531</v>
       </c>
       <c r="B85" t="n">
-        <v>8.92</v>
+        <v>21.44</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
         <v>44562</v>
       </c>
       <c r="B86" t="n">
-        <v>15.6</v>
+        <v>18.01</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>44593</v>
       </c>
       <c r="B87" t="n">
-        <v>13.81</v>
+        <v>17.99</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -1571,9 +1571,7 @@
       <c r="A88" s="2" t="n">
         <v>44621</v>
       </c>
-      <c r="B88" t="n">
-        <v>7.37</v>
-      </c>
+      <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
           <t>CAR</t>
@@ -1584,9 +1582,7 @@
       <c r="A89" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B89" t="n">
-        <v>8.35</v>
-      </c>
+      <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
           <t>CAR</t>
@@ -1597,9 +1593,7 @@
       <c r="A90" s="2" t="n">
         <v>44682</v>
       </c>
-      <c r="B90" t="n">
-        <v>7.84</v>
-      </c>
+      <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
           <t>CAR</t>
@@ -1611,7 +1605,7 @@
         <v>44713</v>
       </c>
       <c r="B91" t="n">
-        <v>7.66</v>
+        <v>16.65</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -1624,7 +1618,7 @@
         <v>44743</v>
       </c>
       <c r="B92" t="n">
-        <v>9.029999999999999</v>
+        <v>17.16</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -1637,7 +1631,7 @@
         <v>44774</v>
       </c>
       <c r="B93" t="n">
-        <v>8.029999999999999</v>
+        <v>17.1</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -1650,7 +1644,7 @@
         <v>44805</v>
       </c>
       <c r="B94" t="n">
-        <v>7.88</v>
+        <v>16.92</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -1663,7 +1657,7 @@
         <v>44835</v>
       </c>
       <c r="B95" t="n">
-        <v>7.09</v>
+        <v>18.85</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -1676,7 +1670,7 @@
         <v>44866</v>
       </c>
       <c r="B96" t="n">
-        <v>9.9</v>
+        <v>18.84</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -1689,7 +1683,7 @@
         <v>44896</v>
       </c>
       <c r="B97" t="n">
-        <v>8.92</v>
+        <v>19.16</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -1702,7 +1696,7 @@
         <v>44927</v>
       </c>
       <c r="B98" t="n">
-        <v>15.6</v>
+        <v>19.68</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -1715,7 +1709,7 @@
         <v>44958</v>
       </c>
       <c r="B99" t="n">
-        <v>13.81</v>
+        <v>19.84</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -1728,7 +1722,7 @@
         <v>44986</v>
       </c>
       <c r="B100" t="n">
-        <v>7.37</v>
+        <v>20.34</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -1741,7 +1735,7 @@
         <v>45017</v>
       </c>
       <c r="B101" t="n">
-        <v>8.35</v>
+        <v>20.8</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -1754,7 +1748,7 @@
         <v>45047</v>
       </c>
       <c r="B102" t="n">
-        <v>7.84</v>
+        <v>20.95</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -1767,7 +1761,7 @@
         <v>45078</v>
       </c>
       <c r="B103" t="n">
-        <v>7.66</v>
+        <v>22.8</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -1780,7 +1774,7 @@
         <v>45108</v>
       </c>
       <c r="B104" t="n">
-        <v>9.029999999999999</v>
+        <v>23.77</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -1793,7 +1787,7 @@
         <v>45139</v>
       </c>
       <c r="B105" t="n">
-        <v>8.029999999999999</v>
+        <v>24.3</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -1806,7 +1800,7 @@
         <v>45170</v>
       </c>
       <c r="B106" t="n">
-        <v>7.88</v>
+        <v>24.94</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -1819,7 +1813,7 @@
         <v>45200</v>
       </c>
       <c r="B107" t="n">
-        <v>7.09</v>
+        <v>24.99</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -1832,7 +1826,7 @@
         <v>45231</v>
       </c>
       <c r="B108" t="n">
-        <v>9.9</v>
+        <v>25.31</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -1845,7 +1839,7 @@
         <v>45261</v>
       </c>
       <c r="B109" t="n">
-        <v>8.92</v>
+        <v>25.41</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -1858,7 +1852,7 @@
         <v>45292</v>
       </c>
       <c r="B110" t="n">
-        <v>15.6</v>
+        <v>21.07</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -1871,7 +1865,7 @@
         <v>45323</v>
       </c>
       <c r="B111" t="n">
-        <v>13.81</v>
+        <v>20.57</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -1884,7 +1878,7 @@
         <v>45352</v>
       </c>
       <c r="B112" t="n">
-        <v>7.37</v>
+        <v>19.98</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -1897,7 +1891,7 @@
         <v>45383</v>
       </c>
       <c r="B113" t="n">
-        <v>8.35</v>
+        <v>20.44</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -1910,7 +1904,7 @@
         <v>45413</v>
       </c>
       <c r="B114" t="n">
-        <v>7.84</v>
+        <v>18.38</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -1923,7 +1917,7 @@
         <v>45444</v>
       </c>
       <c r="B115" t="n">
-        <v>7.66</v>
+        <v>19.07</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -1936,7 +1930,7 @@
         <v>45474</v>
       </c>
       <c r="B116" t="n">
-        <v>9.029999999999999</v>
+        <v>19.07</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -1949,7 +1943,7 @@
         <v>45505</v>
       </c>
       <c r="B117" t="n">
-        <v>8.029999999999999</v>
+        <v>19.85</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -1961,9 +1955,7 @@
       <c r="A118" s="2" t="n">
         <v>45536</v>
       </c>
-      <c r="B118" t="n">
-        <v>7.88</v>
-      </c>
+      <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
           <t>CAR</t>
@@ -1974,9 +1966,7 @@
       <c r="A119" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B119" t="n">
-        <v>7.09</v>
-      </c>
+      <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
           <t>CAR</t>
@@ -1987,9 +1977,7 @@
       <c r="A120" s="2" t="n">
         <v>45597</v>
       </c>
-      <c r="B120" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
           <t>CAR</t>
@@ -2000,9 +1988,7 @@
       <c r="A121" s="2" t="n">
         <v>45627</v>
       </c>
-      <c r="B121" t="n">
-        <v>8.92</v>
-      </c>
+      <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
           <t>CAR</t>
@@ -2014,7 +2000,7 @@
         <v>45658</v>
       </c>
       <c r="B122" t="n">
-        <v>15.6</v>
+        <v>17.35</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -2027,7 +2013,7 @@
         <v>45689</v>
       </c>
       <c r="B123" t="n">
-        <v>13.81</v>
+        <v>16.98</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -2040,7 +2026,7 @@
         <v>45717</v>
       </c>
       <c r="B124" t="n">
-        <v>7.37</v>
+        <v>16.91</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -2053,7 +2039,7 @@
         <v>45748</v>
       </c>
       <c r="B125" t="n">
-        <v>8.35</v>
+        <v>16.23</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -2066,7 +2052,7 @@
         <v>45778</v>
       </c>
       <c r="B126" t="n">
-        <v>7.84</v>
+        <v>15.49</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -2079,7 +2065,7 @@
         <v>45809</v>
       </c>
       <c r="B127" t="n">
-        <v>7.66</v>
+        <v>15.49</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -2092,7 +2078,7 @@
         <v>45839</v>
       </c>
       <c r="B128" t="n">
-        <v>9.029999999999999</v>
+        <v>15.52</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -2105,7 +2091,7 @@
         <v>45870</v>
       </c>
       <c r="B129" t="n">
-        <v>8.029999999999999</v>
+        <v>15.31</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -2118,7 +2104,7 @@
         <v>45901</v>
       </c>
       <c r="B130" t="n">
-        <v>7.88</v>
+        <v>15.02</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -2131,7 +2117,7 @@
         <v>45931</v>
       </c>
       <c r="B131" t="n">
-        <v>7.09</v>
+        <v>15.43</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -2144,7 +2130,7 @@
         <v>45962</v>
       </c>
       <c r="B132" t="n">
-        <v>9.9</v>
+        <v>15.26</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -2157,7 +2143,7 @@
         <v>45992</v>
       </c>
       <c r="B133" t="n">
-        <v>8.92</v>
+        <v>15.08</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
